--- a/output/pdf_financials_xlsx/MANN.xlsx
+++ b/output/pdf_financials_xlsx/MANN.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.251863</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.251863</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.251863</v>
       </c>
     </row>
     <row r="93">
@@ -3017,7 +3017,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3191,7 +3195,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>2.251863</v>
       </c>

--- a/output/pdf_financials_xlsx/MANN.xlsx
+++ b/output/pdf_financials_xlsx/MANN.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000745</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.176531</v>
+        <v>-2.177276</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-8.146266000000001</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.176531</v>
+        <v>-2.177276</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-8.146266000000001</v>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.585833</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.361347</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.037549</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.585833</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.361347</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.037549</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.827873</v>
+        <v>0.24204</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.849549</v>
+        <v>0.488202</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.037966</v>
+        <v>0.000417</v>
       </c>
     </row>
     <row r="49">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
